--- a/src/data/products-data.xlsx
+++ b/src/data/products-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lyanc\VScodeProgram\inteplast_home_page_tw\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39330CFF-DBDC-4DC3-B38C-C77A33C80CB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20725A43-4ED5-4F1E-BCA9-7A707DE1D4C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,9 +25,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
-  <si>
-    <t>產品名稱</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="31">
+  <si>
+    <t>產品</t>
   </si>
   <si>
     <t>英文名稱</t>
@@ -39,25 +39,22 @@
     <t>產品圖片</t>
   </si>
   <si>
-    <t>CAN LINERS &amp; TRASH BAGS</t>
-  </si>
-  <si>
-    <t>連捲、單張抽取與環保清潔袋，台塑原料自製吹膜。</t>
+    <t>產品細項</t>
+  </si>
+  <si>
+    <t>清潔袋</t>
   </si>
   <si>
     <t>封面-清潔袋.png</t>
   </si>
   <si>
-    <t>DRAW-TAPE BAGS</t>
-  </si>
-  <si>
-    <t>一拉即束口，清潔袋與醫療感染袋兩條產線。</t>
+    <t>拉繩袋</t>
   </si>
   <si>
     <t>封面-拉繩袋.png</t>
   </si>
   <si>
-    <t>HEAT-RESISTANT &amp; PRODUCE</t>
+    <t>蔬果袋</t>
   </si>
   <si>
     <t>食品級原料，平裝、捲裝耐熱袋與蔬果袋。</t>
@@ -66,40 +63,72 @@
     <t>封面-蔬果袋.png</t>
   </si>
   <si>
-    <t>STORAGE &amp; ZIPPER BAGS</t>
-  </si>
-  <si>
-    <t>密實袋、立體密實袋、冷凍袋與 00–12 號夾鏈袋。</t>
+    <t>夾鏈袋</t>
+  </si>
+  <si>
+    <t>多功能手套</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Scale Sheet</t>
   </si>
   <si>
     <t>封面-夾鏈袋.png</t>
-  </si>
-  <si>
-    <t>Scale Sheet</t>
-  </si>
-  <si>
-    <t>集團專利抽取式包裝紙，一張接一張自動彈出。</t>
-  </si>
-  <si>
-    <t>scale sheet.png</t>
-  </si>
-  <si>
-    <t>台塑遮蔽防塵膠帶</t>
-  </si>
-  <si>
-    <t>蔬果袋</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>拉繩袋</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>清潔袋</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>夾鏈袋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>封面-scale sheet.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>封面-多功能手套.png</t>
+  </si>
+  <si>
+    <t>遮蔽防塵膠帶</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>封面-台塑遮蔽防塵膠帶.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Draw Tape Liners</t>
+  </si>
+  <si>
+    <t>Can Liners</t>
+  </si>
+  <si>
+    <t>一拉即束口，防止臭味外溢。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>集團專利抽取式秤紙。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>連捲、單張抽取與環保清潔袋。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>密實袋、冷凍袋、夾鏈袋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>耐熱袋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>連捲、單張抽取、環保清潔袋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>清潔袋、醫療袋、環保拉繩袋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>專利證書</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -107,7 +136,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -121,13 +150,6 @@
       <family val="3"/>
       <charset val="136"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="微軟正黑體"/>
-      <family val="2"/>
-      <charset val="136"/>
     </font>
   </fonts>
   <fills count="2">
@@ -150,9 +172,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -492,328 +513,148 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.77734375" customWidth="1"/>
-    <col min="2" max="2" width="36.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="57.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="32.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.77734375" customWidth="1"/>
+    <col min="2" max="2" width="33.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="94.109375" customWidth="1"/>
+    <col min="4" max="4" width="30.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="40.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="E4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="E5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="1" t="s">
+      <c r="E8" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A7 C7:D7 A1:D1 B4:D4 B3:D3 B2:D2" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:E1 A6:C6 A5 A4 E6 D4 D5" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/src/data/products-data.xlsx
+++ b/src/data/products-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lyanc\VScodeProgram\inteplast_home_page_tw\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20725A43-4ED5-4F1E-BCA9-7A707DE1D4C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5C559F2-6D22-45FF-B57E-E9B04B930074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -100,10 +100,6 @@
     <t>Can Liners</t>
   </si>
   <si>
-    <t>一拉即束口，防止臭味外溢。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>集團專利抽取式秤紙。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -129,6 +125,32 @@
   </si>
   <si>
     <t>專利證書</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>一拉即束口</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei UI"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，多30%以上使用容量</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，並可防止臭味外溢。</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -136,7 +158,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -150,6 +172,13 @@
       <family val="3"/>
       <charset val="136"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Microsoft JhengHei UI"/>
+      <family val="2"/>
+      <charset val="136"/>
     </font>
   </fonts>
   <fills count="2">
@@ -548,13 +577,13 @@
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
         <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -568,7 +597,7 @@
         <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -579,13 +608,13 @@
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
         <v>6</v>
       </c>
       <c r="E4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -596,13 +625,13 @@
         <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
         <v>8</v>
       </c>
       <c r="E5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -630,7 +659,7 @@
         <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">

--- a/src/data/products-data.xlsx
+++ b/src/data/products-data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lyanc\VScodeProgram\inteplast_home_page_tw\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5C559F2-6D22-45FF-B57E-E9B04B930074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B17DCD3-4B18-44D6-A364-40CDC3ED99DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="產品資料" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
   <si>
     <t>產品</t>
   </si>
@@ -79,10 +79,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>封面-scale sheet.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>封面-多功能手套.png</t>
   </si>
   <si>
@@ -112,14 +108,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>耐熱袋</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>連捲、單張抽取、環保清潔袋</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>清潔袋、醫療袋、環保拉繩袋</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -128,29 +116,49 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>一拉即束口</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei UI"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>，多30%以上使用容量</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>，並可防止臭味外溢。</t>
-    </r>
+    <t>封面-Scale Sheet.png</t>
+  </si>
+  <si>
+    <t>Produce Bag</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>連捲、單張抽取、八折袋、環保清潔袋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>耐熱袋、食品袋、市場袋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Multifunctional Gloves</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>內壓紋、易穿脫、彈性優、觸感佳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>無粉末、無乳膠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一拉即束口，多30%以上使用容量，並可防止臭味外溢。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Recloseable Zipper Bags</t>
+  </si>
+  <si>
+    <t>遮蔽保護、消毒防護、覆蓋防塵、施工便利</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>手感扎實、夾鏈緊密、多次使用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pre-Taped Masking Film</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -158,7 +166,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -176,9 +184,15 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Microsoft JhengHei UI"/>
+      <name val="微軟正黑體"/>
       <family val="2"/>
       <charset val="136"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF3C535D"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -201,8 +215,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -543,139 +564,149 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.77734375" customWidth="1"/>
-    <col min="2" max="2" width="33.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="94.109375" customWidth="1"/>
-    <col min="4" max="4" width="30.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="40.77734375" customWidth="1"/>
+    <col min="1" max="1" width="20.77734375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="61.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="48.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" t="s">
-        <v>29</v>
+      <c r="C2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E3" t="s">
-        <v>26</v>
+      <c r="E3" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="B4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E4" t="s">
-        <v>27</v>
+      <c r="E4" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="B5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E5" t="s">
-        <v>28</v>
+      <c r="E5" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" t="s">
-        <v>14</v>
+      <c r="B6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D7" t="s">
+      <c r="B7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E7" t="s">
-        <v>25</v>
+      <c r="E7" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="A8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="E8" s="1" t="s">
         <v>14</v>
       </c>
     </row>
@@ -683,7 +714,7 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:E1 A6:C6 A5 A4 E6 D4 D5" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:E1 A6 A5 A4 D4 D5" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/src/data/products-data.xlsx
+++ b/src/data/products-data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lyanc\VScodeProgram\inteplast_home_page_tw\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B17DCD3-4B18-44D6-A364-40CDC3ED99DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{975C0869-C802-46F5-9353-B786DB90E1E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="產品資料" sheetId="1" r:id="rId1"/>
@@ -127,10 +127,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>耐熱袋、食品袋、市場袋</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Multifunctional Gloves</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -159,6 +155,32 @@
   </si>
   <si>
     <t>Pre-Taped Masking Film</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>耐熱袋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei UI"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>、雙道封口</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>、食品袋、市場袋</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -166,7 +188,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -193,6 +215,13 @@
       <color rgb="FF3C535D"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Microsoft JhengHei UI"/>
+      <family val="2"/>
+      <charset val="136"/>
     </font>
   </fonts>
   <fills count="2">
@@ -622,7 +651,7 @@
         <v>11</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -650,7 +679,7 @@
         <v>20</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>8</v>
@@ -664,16 +693,16 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -681,10 +710,10 @@
         <v>12</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>16</v>
@@ -698,10 +727,10 @@
         <v>18</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>19</v>

--- a/src/data/products-data.xlsx
+++ b/src/data/products-data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lyanc\VScodeProgram\inteplast_home_page_tw\src\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lyanc\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{975C0869-C802-46F5-9353-B786DB90E1E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{413DDD4D-F556-4EB5-A2B6-868A32C835E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="47">
   <si>
     <t>產品</t>
   </si>
@@ -33,6 +33,9 @@
     <t>英文名稱</t>
   </si>
   <si>
+    <t>重點</t>
+  </si>
+  <si>
     <t>產品敘述</t>
   </si>
   <si>
@@ -57,9 +60,6 @@
     <t>蔬果袋</t>
   </si>
   <si>
-    <t>食品級原料，平裝、捲裝耐熱袋與蔬果袋。</t>
-  </si>
-  <si>
     <t>封面-蔬果袋.png</t>
   </si>
   <si>
@@ -69,132 +69,153 @@
     <t>多功能手套</t>
   </si>
   <si>
-    <t/>
+    <t>封面-Scale Sheet.png</t>
+  </si>
+  <si>
+    <t>專利證書</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Produce Bag</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>耐熱袋、雙道封口、食品袋、市場袋</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Can Liners</t>
+  </si>
+  <si>
+    <t>連捲、單張抽取、八折袋、環保清潔袋</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Draw Tape Liners</t>
+  </si>
+  <si>
+    <t>清潔袋、醫療袋、環保拉繩袋</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Multifunctional Gloves</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>封面-多功能手套.png</t>
+  </si>
+  <si>
+    <t>無粉末、無乳膠、內壓紋、易穿脫、彈性優、觸感佳</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Recloseable Zipper Bags</t>
+  </si>
+  <si>
+    <t>封面-夾鏈袋.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>密實袋、冷凍袋、夾鏈袋</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>遮蔽防塵膠帶</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pre-Taped Masking Film</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>封面-台塑遮蔽防塵膠帶.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>遮蔽保護、消毒防護、覆蓋防塵、施工便利</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Scale Sheet</t>
-  </si>
-  <si>
-    <t>封面-夾鏈袋.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>封面-多功能手套.png</t>
-  </si>
-  <si>
-    <t>遮蔽防塵膠帶</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>封面-台塑遮蔽防塵膠帶.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Draw Tape Liners</t>
-  </si>
-  <si>
-    <t>Can Liners</t>
-  </si>
-  <si>
-    <t>集團專利抽取式秤紙。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>連捲、單張抽取與環保清潔袋。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>密實袋、冷凍袋、夾鏈袋</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>清潔袋、醫療袋、環保拉繩袋</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>專利證書</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>封面-Scale Sheet.png</t>
-  </si>
-  <si>
-    <t>Produce Bag</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>連捲、單張抽取、八折袋、環保清潔袋</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Multifunctional Gloves</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>內壓紋、易穿脫、彈性優、觸感佳</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>無粉末、無乳膠</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>一拉即束口，多30%以上使用容量，並可防止臭味外溢。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Recloseable Zipper Bags</t>
-  </si>
-  <si>
-    <t>遮蔽保護、消毒防護、覆蓋防塵、施工便利</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>手感扎實、夾鏈緊密、多次使用</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Pre-Taped Masking Film</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>耐熱袋</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei UI"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>、雙道封口</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>、食品袋、市場袋</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>一拉即束口，容量大升級增加 30% 、乾淨不沾手</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>專為現代便利生活與高效清潔設計的貼心之作。一體成型的堅固拉繩結構，讓您輕鬆一拉即可俐落束口，有效避免清理時垃圾外漏與雙手沾染髒汙的困擾。特殊設計使內部空間有效利用率增加 30% 以上，並能緊密鎖住異味不外散；另提供醫療級與環保拉繩款式，讓居家與商辦環境更顯潔淨衛生。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>兼具極佳彈性與細緻觸感的多功能手套系列。表面採特殊內壓紋設計，不僅穿脫滑順、不沾黏，更具備良好的防滑抓握力。全系列符合無粉末、無乳膠等友善肌膚標準，無論是用於餐飲調理、食品加工、日常清潔打掃或居家照護，皆能提供全方位且靈活舒適的衛生防護體驗。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>親膚舒適、防護俐落的萬用防護手套</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+結合集團專利技術打造的抽取式 Scale Sheet，打破傳統取用的繁瑣與不便。採用貼心的單張抽取設計，不僅取用俐落、大幅節省作業時間，更能有效管控使用成本。質地強韌、防沾黏且不易破損，是生鮮秤重、餐飲備料、工業分裝及各大商場櫃台追求高效率作業的不可或缺的專業首選。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tare Sheet，集團專利抽取式設計，極致提升效率</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>強韌耐穿刺、滴水不漏的日常清潔首選</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>依託台塑高品質原料自製優勢，經由嘉義新港廠區自動化精密吹膜與封口技術打造。全系列涵蓋連捲式、單張抽取式及國家環保標章認證清潔袋等多種款式。具備超強的抗拉張力與優異承重力，不論是用於一般家庭日常垃圾清運，或是辦公大樓、餐飲旅宿等高頻率商用場域，皆能輕鬆應對、安心不破漏。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>食品級安心原料，守護食材新鮮與衛生</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>專為生鮮食品與日常零售打造的優質蔬果袋系列。嚴選食品級合格原料，質地安全、無毒無味，具備極佳的透明度與抗拉韌性。提供平裝、捲裝等多樣化規格，搭配耐熱袋、雙道封口食品袋及市場專用袋等多元選擇，有效鎖住食材水分與鮮度，為消費者與商家嚴格把關每一道飲食安全防線。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+採用高標準工藝打造的重覆使用夾鏈袋系列。袋身厚實、手感紮實，搭配密合度極佳的雙軌或單軌夾鏈結構，具備優異的氣密與防潮表現。不論是生鮮食材冷凍保鮮、日常小物分類收納，或是工業零件包裝，皆能提供卓越的密封保護，支援多次重複開合依然緊密如初。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>手感紮實、密封緊密，完美鎖住鮮度與整潔</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+集膠帶與防塵膜於一體的便利防護方案。專為室內裝潢、噴漆粉刷、居家裝修及醫療消毒防護設計，能夠快速且大面積地覆蓋並保護傢俱、地板與牆面免受粉塵、油漆噴濺汙染。黏貼穩固且撕除不留殘膠，大幅簡化施工前的遮蔽前置作業，兼具高效率與完美防護效果。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>施工裝潢與日常防塵的省時利器</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Noto Serif HK Medium"/>
+      <family val="1"/>
+      <charset val="136"/>
     </font>
     <font>
       <sz val="9"/>
@@ -206,21 +227,8 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="微軟正黑體"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF3C535D"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Microsoft JhengHei UI"/>
-      <family val="2"/>
+      <name val="Noto Serif HK Medium"/>
+      <family val="1"/>
       <charset val="136"/>
     </font>
   </fonts>
@@ -244,14 +252,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -592,158 +606,191 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.77734375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="30.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="61.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="48.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="16.21875" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.88671875" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="57.44140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="88" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="59.88671875" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="46.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7" ht="19.8" x14ac:dyDescent="0.5">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="99" x14ac:dyDescent="0.5">
       <c r="A2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="G2" s="3"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="79.2" x14ac:dyDescent="0.5">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>38</v>
-      </c>
+      <c r="F3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="3"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="79.2" x14ac:dyDescent="0.5">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>6</v>
+        <v>18</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>40</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="3"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="79.2" x14ac:dyDescent="0.5">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>8</v>
+      <c r="D5" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>25</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="3"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="79.2" x14ac:dyDescent="0.5">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>17</v>
+      <c r="B6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>32</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="3"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="99" x14ac:dyDescent="0.5">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>16</v>
+      <c r="B7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>24</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="3"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="99" x14ac:dyDescent="0.5">
       <c r="A8" s="1" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>19</v>
+        <v>29</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>14</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8" s="3"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:E1 A6 A5 A4 D4 D5" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:F1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/src/data/products-data.xlsx
+++ b/src/data/products-data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lyanc\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lyanc\VScodeProgram\inteplast_home_page_tw\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{413DDD4D-F556-4EB5-A2B6-868A32C835E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43C8A870-F98A-4815-B4F9-2591C256764B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -156,11 +156,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">
-結合集團專利技術打造的抽取式 Scale Sheet，打破傳統取用的繁瑣與不便。採用貼心的單張抽取設計，不僅取用俐落、大幅節省作業時間，更能有效管控使用成本。質地強韌、防沾黏且不易破損，是生鮮秤重、餐飲備料、工業分裝及各大商場櫃台追求高效率作業的不可或缺的專業首選。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Tare Sheet，集團專利抽取式設計，極致提升效率</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -174,10 +169,6 @@
   </si>
   <si>
     <t>食品級安心原料，守護食材新鮮與衛生</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>專為生鮮食品與日常零售打造的優質蔬果袋系列。嚴選食品級合格原料，質地安全、無毒無味，具備極佳的透明度與抗拉韌性。提供平裝、捲裝等多樣化規格，搭配耐熱袋、雙道封口食品袋及市場專用袋等多元選擇，有效鎖住食材水分與鮮度，為消費者與商家嚴格把關每一道飲食安全防線。</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -196,6 +187,14 @@
   </si>
   <si>
     <t>施工裝潢與日常防塵的省時利器</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>結合集團專利技術打造的抽取式 Scale Sheet，打破傳統取用的繁瑣與不便。採用貼心的單張抽取設計，不僅取用俐落、大幅節省作業時間，更能有效管控使用成本。質地強韌、防沾黏且不易破損，是生鮮秤重、餐飲備料、工業分裝及各大商場櫃台追求高效率作業的不可或缺的專業首選。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>專為生鮮食品與日常零售打造的優質蔬果袋系列。嚴選食品級合格原料，質地安全、無毒無味，具備極佳的抗拉韌性。提供平裝、捲裝等多樣化規格，搭配耐熱袋、雙道封口食品袋及市場專用袋等多元選擇，有效鎖住食材水分與鮮度，為消費者與商家嚴格把關每一道飲食安全防線。</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -639,7 +638,7 @@
       </c>
       <c r="G1" s="3"/>
     </row>
-    <row r="2" spans="1:7" ht="99" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:7" ht="79.2" x14ac:dyDescent="0.5">
       <c r="A2" s="1" t="s">
         <v>32</v>
       </c>
@@ -647,10 +646,10 @@
         <v>32</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>14</v>
@@ -668,10 +667,10 @@
         <v>16</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>11</v>
@@ -689,10 +688,10 @@
         <v>18</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>7</v>
@@ -752,10 +751,10 @@
         <v>25</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>26</v>
@@ -773,10 +772,10 @@
         <v>29</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>30</v>

--- a/src/data/products-data.xlsx
+++ b/src/data/products-data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lyanc\VScodeProgram\inteplast_home_page_tw\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43C8A870-F98A-4815-B4F9-2591C256764B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC71CDFA-6B6F-4623-BB90-B8EB648007D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="產品資料" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="52">
   <si>
     <t>產品</t>
   </si>
@@ -36,185 +36,165 @@
     <t>重點</t>
   </si>
   <si>
+    <t>重點英文</t>
+  </si>
+  <si>
     <t>產品敘述</t>
   </si>
   <si>
+    <t>產品敘述英文</t>
+  </si>
+  <si>
     <t>產品圖片</t>
   </si>
   <si>
     <t>產品細項</t>
   </si>
   <si>
+    <t>產品細項英文</t>
+  </si>
+  <si>
+    <t>Scale Sheet</t>
+  </si>
+  <si>
+    <t>Tare Sheet，集團專利抽取式設計，極致提升效率</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>結合集團專利技術打造的抽取式 Scale Sheet，打破傳統取用的繁瑣與不便。採用貼心的單張抽取設計，不僅取用俐落、大幅節省作業時間，更能有效管控使用成本。質地強韌、防沾黏且不易破損，是生鮮秤重、餐飲備料、工業分裝及各大商場櫃台追求高效率作業的不可或缺的專業首選。</t>
+  </si>
+  <si>
+    <t>封面-Scale Sheet.png</t>
+  </si>
+  <si>
+    <t>專利證書</t>
+  </si>
+  <si>
+    <t>蔬果袋</t>
+  </si>
+  <si>
+    <t>Produce Bag</t>
+  </si>
+  <si>
+    <t>食品級安心原料，守護食材新鮮與衛生</t>
+  </si>
+  <si>
+    <t>專為生鮮食品與日常零售打造的優質蔬果袋系列。嚴選食品級合格原料，質地安全、無毒無味，具備極佳的抗拉韌性。提供平裝、捲裝等多樣化規格，搭配耐熱袋、雙道封口食品袋及市場專用袋等多元選擇，有效鎖住食材水分與鮮度，為消費者與商家嚴格把關每一道飲食安全防線。</t>
+  </si>
+  <si>
+    <t>封面-蔬果袋.png</t>
+  </si>
+  <si>
+    <t>耐熱袋、雙道封口、食品袋、市場袋</t>
+  </si>
+  <si>
     <t>清潔袋</t>
   </si>
   <si>
+    <t>Can Liners</t>
+  </si>
+  <si>
+    <t>強韌耐穿刺、滴水不漏的日常清潔首選</t>
+  </si>
+  <si>
+    <t>依託台塑高品質原料自製優勢，經由嘉義新港廠區自動化精密吹膜與封口技術打造。全系列涵蓋連捲式、單張抽取式及國家環保標章認證清潔袋等多種款式。具備超強的抗拉張力與優異承重力，不論是用於一般家庭日常垃圾清運，或是辦公大樓、餐飲旅宿等高頻率商用場域，皆能輕鬆應對、安心不破漏。</t>
+  </si>
+  <si>
     <t>封面-清潔袋.png</t>
   </si>
   <si>
+    <t>連捲、單張抽取、八折袋、環保清潔袋</t>
+  </si>
+  <si>
     <t>拉繩袋</t>
   </si>
   <si>
+    <t>Draw Tape Liners</t>
+  </si>
+  <si>
+    <t>一拉即束口，容量大升級增加 30% 、乾淨不沾手</t>
+  </si>
+  <si>
+    <t>專為現代便利生活與高效清潔設計的貼心之作。一體成型的堅固拉繩結構，讓您輕鬆一拉即可俐落束口，有效避免清理時垃圾外漏與雙手沾染髒汙的困擾。特殊設計使內部空間有效利用率增加 30% 以上，並能緊密鎖住異味不外散；另提供醫療級與環保拉繩款式，讓居家與商辦環境更顯潔淨衛生。</t>
+  </si>
+  <si>
     <t>封面-拉繩袋.png</t>
   </si>
   <si>
-    <t>蔬果袋</t>
-  </si>
-  <si>
-    <t>封面-蔬果袋.png</t>
+    <t>清潔袋、醫療袋、環保拉繩袋</t>
+  </si>
+  <si>
+    <t>多功能手套</t>
+  </si>
+  <si>
+    <t>Multifunctional Gloves</t>
+  </si>
+  <si>
+    <t>親膚舒適、防護俐落的萬用防護手套</t>
+  </si>
+  <si>
+    <t>兼具極佳彈性與細緻觸感的多功能手套系列。表面採特殊內壓紋設計，不僅穿脫滑順、不沾黏，更具備良好的防滑抓握力。全系列符合無粉末、無乳膠等友善肌膚標準，無論是用於餐飲調理、食品加工、日常清潔打掃或居家照護，皆能提供全方位且靈活舒適的衛生防護體驗。</t>
+  </si>
+  <si>
+    <t>封面-多功能手套.png</t>
+  </si>
+  <si>
+    <t>無粉末、無乳膠、內壓紋、易穿脫、彈性優、觸感佳</t>
   </si>
   <si>
     <t>夾鏈袋</t>
   </si>
   <si>
-    <t>多功能手套</t>
-  </si>
-  <si>
-    <t>封面-Scale Sheet.png</t>
-  </si>
-  <si>
-    <t>專利證書</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Produce Bag</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>耐熱袋、雙道封口、食品袋、市場袋</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Can Liners</t>
-  </si>
-  <si>
-    <t>連捲、單張抽取、八折袋、環保清潔袋</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Draw Tape Liners</t>
-  </si>
-  <si>
-    <t>清潔袋、醫療袋、環保拉繩袋</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Multifunctional Gloves</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>封面-多功能手套.png</t>
-  </si>
-  <si>
-    <t>無粉末、無乳膠、內壓紋、易穿脫、彈性優、觸感佳</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Recloseable Zipper Bags</t>
   </si>
   <si>
+    <t>手感紮實、密封緊密，完美鎖住鮮度與整潔</t>
+  </si>
+  <si>
+    <t>採用高標準工藝打造的重覆使用夾鏈袋系列。袋身厚實、手感紮實，搭配密合度極佳的雙軌或單軌夾鏈結構，具備優異的氣密與防潮表現。不論是生鮮食材冷凍保鮮、日常小物分類收納，或是工業零件包裝，皆能提供卓越的密封保護，支援多次重複開合依然緊密如初。</t>
+  </si>
+  <si>
     <t>封面-夾鏈袋.png</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>密實袋、冷凍袋、夾鏈袋</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>遮蔽防塵膠帶</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Pre-Taped Masking Film</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>施工裝潢與日常防塵的省時利器</t>
+  </si>
+  <si>
+    <t>集膠帶與防塵膜於一體的便利防護方案。專為室內裝潢、噴漆粉刷、居家裝修及醫療消毒防護設計，能夠快速且大面積地覆蓋並保護傢俱、地板與牆面免受粉塵、油漆噴濺汙染。黏貼穩固且撕除不留殘膠，大幅簡化施工前的遮蔽前置作業，兼具高效率與完美防護效果。</t>
   </si>
   <si>
     <t>封面-台塑遮蔽防塵膠帶.png</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>遮蔽保護、消毒防護、覆蓋防塵、施工便利</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Scale Sheet</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>一拉即束口，容量大升級增加 30% 、乾淨不沾手</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>專為現代便利生活與高效清潔設計的貼心之作。一體成型的堅固拉繩結構，讓您輕鬆一拉即可俐落束口，有效避免清理時垃圾外漏與雙手沾染髒汙的困擾。特殊設計使內部空間有效利用率增加 30% 以上，並能緊密鎖住異味不外散；另提供醫療級與環保拉繩款式，讓居家與商辦環境更顯潔淨衛生。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>兼具極佳彈性與細緻觸感的多功能手套系列。表面採特殊內壓紋設計，不僅穿脫滑順、不沾黏，更具備良好的防滑抓握力。全系列符合無粉末、無乳膠等友善肌膚標準，無論是用於餐飲調理、食品加工、日常清潔打掃或居家照護，皆能提供全方位且靈活舒適的衛生防護體驗。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>親膚舒適、防護俐落的萬用防護手套</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tare Sheet，集團專利抽取式設計，極致提升效率</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>強韌耐穿刺、滴水不漏的日常清潔首選</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>依託台塑高品質原料自製優勢，經由嘉義新港廠區自動化精密吹膜與封口技術打造。全系列涵蓋連捲式、單張抽取式及國家環保標章認證清潔袋等多種款式。具備超強的抗拉張力與優異承重力，不論是用於一般家庭日常垃圾清運，或是辦公大樓、餐飲旅宿等高頻率商用場域，皆能輕鬆應對、安心不破漏。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>食品級安心原料，守護食材新鮮與衛生</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">
-採用高標準工藝打造的重覆使用夾鏈袋系列。袋身厚實、手感紮實，搭配密合度極佳的雙軌或單軌夾鏈結構，具備優異的氣密與防潮表現。不論是生鮮食材冷凍保鮮、日常小物分類收納，或是工業零件包裝，皆能提供卓越的密封保護，支援多次重複開合依然緊密如初。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>手感紮實、密封緊密，完美鎖住鮮度與整潔</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">
-集膠帶與防塵膜於一體的便利防護方案。專為室內裝潢、噴漆粉刷、居家裝修及醫療消毒防護設計，能夠快速且大面積地覆蓋並保護傢俱、地板與牆面免受粉塵、油漆噴濺汙染。黏貼穩固且撕除不留殘膠，大幅簡化施工前的遮蔽前置作業，兼具高效率與完美防護效果。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>施工裝潢與日常防塵的省時利器</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>結合集團專利技術打造的抽取式 Scale Sheet，打破傳統取用的繁瑣與不便。採用貼心的單張抽取設計，不僅取用俐落、大幅節省作業時間，更能有效管控使用成本。質地強韌、防沾黏且不易破損，是生鮮秤重、餐飲備料、工業分裝及各大商場櫃台追求高效率作業的不可或缺的專業首選。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>專為生鮮食品與日常零售打造的優質蔬果袋系列。嚴選食品級合格原料，質地安全、無毒無味，具備極佳的抗拉韌性。提供平裝、捲裝等多樣化規格，搭配耐熱袋、雙道封口食品袋及市場專用袋等多元選擇，有效鎖住食材水分與鮮度，為消費者與商家嚴格把關每一道飲食安全防線。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Scale Sheet(Tare Sheet)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Noto Serif HK Medium"/>
-      <family val="1"/>
-      <charset val="136"/>
     </font>
     <font>
       <sz val="9"/>
@@ -226,8 +206,8 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Noto Serif HK Medium"/>
-      <family val="1"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
       <charset val="136"/>
     </font>
   </fonts>
@@ -251,21 +231,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -605,191 +573,258 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.21875" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31.88671875" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="57.44140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="88" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="33" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="59.88671875" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="46.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.77734375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="28.77734375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="40.77734375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="44.77734375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="46.77734375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="50.77734375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="29.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="44.77734375" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="19.8" x14ac:dyDescent="0.5">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3"/>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:7" ht="79.2" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>45</v>
+        <v>51</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="I2" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="G2" s="3"/>
-    </row>
-    <row r="3" spans="1:7" ht="79.2" x14ac:dyDescent="0.5">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="C7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="3"/>
-    </row>
-    <row r="4" spans="1:7" ht="79.2" x14ac:dyDescent="0.5">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G4" s="3"/>
-    </row>
-    <row r="5" spans="1:7" ht="79.2" x14ac:dyDescent="0.5">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" s="3"/>
-    </row>
-    <row r="6" spans="1:7" ht="79.2" x14ac:dyDescent="0.5">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G6" s="3"/>
-    </row>
-    <row r="7" spans="1:7" ht="99" x14ac:dyDescent="0.5">
-      <c r="A7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G7" s="3"/>
-    </row>
-    <row r="8" spans="1:7" ht="99" x14ac:dyDescent="0.5">
-      <c r="A8" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>43</v>
+      <c r="C8" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G8" s="3"/>
+        <v>11</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:F1" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:I1 A3:I8 A2 C2:I2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/src/data/products-data.xlsx
+++ b/src/data/products-data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lyanc\VScodeProgram\inteplast_home_page_tw\src\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lyanc\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC71CDFA-6B6F-4623-BB90-B8EB648007D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAD0C6E9-5303-40B0-95EC-D8DDB9911411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="產品資料" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="71">
   <si>
     <t>產品</t>
   </si>
@@ -60,18 +60,24 @@
     <t>Tare Sheet，集團專利抽取式設計，極致提升效率</t>
   </si>
   <si>
-    <t/>
+    <t>Tare Sheet: group-patented pop-up design for faster weighing</t>
   </si>
   <si>
     <t>結合集團專利技術打造的抽取式 Scale Sheet，打破傳統取用的繁瑣與不便。採用貼心的單張抽取設計，不僅取用俐落、大幅節省作業時間，更能有效管控使用成本。質地強韌、防沾黏且不易破損，是生鮮秤重、餐飲備料、工業分裝及各大商場櫃台追求高效率作業的不可或缺的專業首選。</t>
   </si>
   <si>
+    <t>A pop-up Scale Sheet built on Inteplast Group patented technology, replacing the fumbling of conventional sheet stacks. Single-sheet dispensing keeps handling quick, cuts labour time and keeps consumption under control. Tough, non-stick and tear-resistant, it is the professional choice for fresh-food weighing, kitchen prep, industrial repacking and high-volume retail counters.</t>
+  </si>
+  <si>
     <t>封面-Scale Sheet.png</t>
   </si>
   <si>
     <t>專利證書</t>
   </si>
   <si>
+    <t>Patent certificate</t>
+  </si>
+  <si>
     <t>蔬果袋</t>
   </si>
   <si>
@@ -81,15 +87,24 @@
     <t>食品級安心原料，守護食材新鮮與衛生</t>
   </si>
   <si>
+    <t>Food-grade resin that keeps produce fresh and hygienic</t>
+  </si>
+  <si>
     <t>專為生鮮食品與日常零售打造的優質蔬果袋系列。嚴選食品級合格原料，質地安全、無毒無味，具備極佳的抗拉韌性。提供平裝、捲裝等多樣化規格，搭配耐熱袋、雙道封口食品袋及市場專用袋等多元選擇，有效鎖住食材水分與鮮度，為消費者與商家嚴格把關每一道飲食安全防線。</t>
   </si>
   <si>
+    <t>A premium produce bag range for fresh food and everyday retail. Made from certified food-grade resin that is safe, odourless and highly tear-resistant. Available flat-packed or on the roll, with heat-resistant bags, double-sealed food bags and market bags to choose from, locking in moisture and freshness so shoppers and store owners can rely on every layer of food safety.</t>
+  </si>
+  <si>
     <t>封面-蔬果袋.png</t>
   </si>
   <si>
     <t>耐熱袋、雙道封口、食品袋、市場袋</t>
   </si>
   <si>
+    <t>Heat-resistant bag, Double seal, Food bag, Market bag</t>
+  </si>
+  <si>
     <t>清潔袋</t>
   </si>
   <si>
@@ -99,15 +114,24 @@
     <t>強韌耐穿刺、滴水不漏的日常清潔首選</t>
   </si>
   <si>
+    <t>Puncture-resistant, leak-proof, built for everyday waste</t>
+  </si>
+  <si>
     <t>依託台塑高品質原料自製優勢，經由嘉義新港廠區自動化精密吹膜與封口技術打造。全系列涵蓋連捲式、單張抽取式及國家環保標章認證清潔袋等多種款式。具備超強的抗拉張力與優異承重力，不論是用於一般家庭日常垃圾清運，或是辦公大樓、餐飲旅宿等高頻率商用場域，皆能輕鬆應對、安心不破漏。</t>
   </si>
   <si>
+    <t>Produced in-house from premium Formosa Plastics resin, using automated precision extrusion and sealing at our Xingang plant in Chiayi. The range covers perforated rolls, single-sheet dispensing and Green Mark certified liners. High tensile strength and load capacity handle both household waste and the high turnover of office buildings, restaurants and hotels without splitting or leaking.</t>
+  </si>
+  <si>
     <t>封面-清潔袋.png</t>
   </si>
   <si>
     <t>連捲、單張抽取、八折袋、環保清潔袋</t>
   </si>
   <si>
+    <t>Perforated roll, Single-sheet dispensing, Eight-fold gusseted bag, Green Mark liner</t>
+  </si>
+  <si>
     <t>拉繩袋</t>
   </si>
   <si>
@@ -117,15 +141,24 @@
     <t>一拉即束口，容量大升級增加 30% 、乾淨不沾手</t>
   </si>
   <si>
+    <t>One pull closes the bag, with 30% more capacity and no mess on your hands</t>
+  </si>
+  <si>
     <t>專為現代便利生活與高效清潔設計的貼心之作。一體成型的堅固拉繩結構，讓您輕鬆一拉即可俐落束口，有效避免清理時垃圾外漏與雙手沾染髒汙的困擾。特殊設計使內部空間有效利用率增加 30% 以上，並能緊密鎖住異味不外散；另提供醫療級與環保拉繩款式，讓居家與商辦環境更顯潔淨衛生。</t>
   </si>
   <si>
+    <t>Designed for convenience and fast clean-up. The one-piece draw tape closes the bag with a single pull, so waste stays inside and hands stay clean. The construction adds over 30% usable capacity while sealing odours in. Medical-grade and eco draw-tape versions are also available, keeping homes and commercial premises visibly cleaner.</t>
+  </si>
+  <si>
     <t>封面-拉繩袋.png</t>
   </si>
   <si>
     <t>清潔袋、醫療袋、環保拉繩袋</t>
   </si>
   <si>
+    <t>Can liner, Medical waste bag, Eco draw tape liner</t>
+  </si>
+  <si>
     <t>多功能手套</t>
   </si>
   <si>
@@ -135,15 +168,24 @@
     <t>親膚舒適、防護俐落的萬用防護手套</t>
   </si>
   <si>
+    <t>Skin-friendly comfort with clean, reliable protection</t>
+  </si>
+  <si>
     <t>兼具極佳彈性與細緻觸感的多功能手套系列。表面採特殊內壓紋設計，不僅穿脫滑順、不沾黏，更具備良好的防滑抓握力。全系列符合無粉末、無乳膠等友善肌膚標準，無論是用於餐飲調理、食品加工、日常清潔打掃或居家照護，皆能提供全方位且靈活舒適的衛生防護體驗。</t>
   </si>
   <si>
+    <t>A multi-purpose glove range combining high elasticity with a fine surface feel. The embossed inner texture makes them easy to put on and take off without sticking, while improving grip. Powder-free and latex-free throughout, they suit food preparation and processing, everyday cleaning and home care, staying flexible, comfortable and hygienic.</t>
+  </si>
+  <si>
     <t>封面-多功能手套.png</t>
   </si>
   <si>
     <t>無粉末、無乳膠、內壓紋、易穿脫、彈性優、觸感佳</t>
   </si>
   <si>
+    <t>Powder-free, Latex-free, Embossed texture, Easy on/off, High elasticity, Soft feel</t>
+  </si>
+  <si>
     <t>夾鏈袋</t>
   </si>
   <si>
@@ -153,15 +195,24 @@
     <t>手感紮實、密封緊密，完美鎖住鮮度與整潔</t>
   </si>
   <si>
+    <t>Solid feel and a tight seal that locks in freshness</t>
+  </si>
+  <si>
     <t>採用高標準工藝打造的重覆使用夾鏈袋系列。袋身厚實、手感紮實，搭配密合度極佳的雙軌或單軌夾鏈結構，具備優異的氣密與防潮表現。不論是生鮮食材冷凍保鮮、日常小物分類收納，或是工業零件包裝，皆能提供卓越的密封保護，支援多次重複開合依然緊密如初。</t>
   </si>
   <si>
+    <t>A reusable zipper bag range made to a high manufacturing standard. Thick-gauge film with single- or double-track zippers delivers excellent airtight and moisture protection. Whether freezing fresh ingredients, sorting everyday items or packing industrial parts, the seal stays tight through repeated opening and closing.</t>
+  </si>
+  <si>
     <t>封面-夾鏈袋.png</t>
   </si>
   <si>
     <t>密實袋、冷凍袋、夾鏈袋</t>
   </si>
   <si>
+    <t>Storage bag, Freezer bag, Zipper bag</t>
+  </si>
+  <si>
     <t>遮蔽防塵膠帶</t>
   </si>
   <si>
@@ -171,17 +222,22 @@
     <t>施工裝潢與日常防塵的省時利器</t>
   </si>
   <si>
+    <t>A time-saver for renovation work and everyday dust protection</t>
+  </si>
+  <si>
     <t>集膠帶與防塵膜於一體的便利防護方案。專為室內裝潢、噴漆粉刷、居家裝修及醫療消毒防護設計，能夠快速且大面積地覆蓋並保護傢俱、地板與牆面免受粉塵、油漆噴濺汙染。黏貼穩固且撕除不留殘膠，大幅簡化施工前的遮蔽前置作業，兼具高效率與完美防護效果。</t>
   </si>
   <si>
+    <t>Masking tape and dust film in one. Made for interior decoration, spray painting, home renovation and medical disinfection screening, it covers large areas fast and protects furniture, floors and walls from dust and overspray. It adheres firmly and removes without residue, cutting masking preparation time while delivering complete protection.</t>
+  </si>
+  <si>
     <t>封面-台塑遮蔽防塵膠帶.png</t>
   </si>
   <si>
     <t>遮蔽保護、消毒防護、覆蓋防塵、施工便利</t>
   </si>
   <si>
-    <t>Scale Sheet(Tare Sheet)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>Masking protection, Disinfection screening, Dust cover, Fast application</t>
   </si>
 </sst>
 </file>
@@ -231,9 +287,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -574,55 +641,54 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I8"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.77734375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="28.77734375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="40.77734375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="44.77734375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="46.77734375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="50.77734375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="29.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="56.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="44.77734375" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="15.33203125" customWidth="1"/>
+    <col min="2" max="2" width="17.77734375" customWidth="1"/>
+    <col min="3" max="3" width="29.6640625" customWidth="1"/>
+    <col min="4" max="4" width="31.44140625" customWidth="1"/>
+    <col min="5" max="5" width="81" customWidth="1"/>
+    <col min="6" max="6" width="90" customWidth="1"/>
+    <col min="7" max="7" width="13.44140625" customWidth="1"/>
+    <col min="8" max="8" width="20.44140625" customWidth="1"/>
+    <col min="9" max="9" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" s="2" customFormat="1" ht="78" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>10</v>
@@ -634,197 +700,197 @@
         <v>12</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" s="2" customFormat="1" ht="78" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" s="2" customFormat="1" ht="78" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" s="2" customFormat="1" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>11</v>
+        <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" s="2" customFormat="1" ht="78" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>11</v>
+        <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" s="2" customFormat="1" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>11</v>
+        <v>58</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>11</v>
+        <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" s="2" customFormat="1" ht="78" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>11</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:I1 A3:I8 A2 C2:I2" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:I8" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/src/data/products-data.xlsx
+++ b/src/data/products-data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lyanc\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lyanc\VScodeProgram\inteplast_home_page_tw\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAD0C6E9-5303-40B0-95EC-D8DDB9911411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51D752CB-EF9D-4A90-800A-0778F44FE35A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,21 +54,6 @@
     <t>產品細項英文</t>
   </si>
   <si>
-    <t>Scale Sheet</t>
-  </si>
-  <si>
-    <t>Tare Sheet，集團專利抽取式設計，極致提升效率</t>
-  </si>
-  <si>
-    <t>Tare Sheet: group-patented pop-up design for faster weighing</t>
-  </si>
-  <si>
-    <t>結合集團專利技術打造的抽取式 Scale Sheet，打破傳統取用的繁瑣與不便。採用貼心的單張抽取設計，不僅取用俐落、大幅節省作業時間，更能有效管控使用成本。質地強韌、防沾黏且不易破損，是生鮮秤重、餐飲備料、工業分裝及各大商場櫃台追求高效率作業的不可或缺的專業首選。</t>
-  </si>
-  <si>
-    <t>A pop-up Scale Sheet built on Inteplast Group patented technology, replacing the fumbling of conventional sheet stacks. Single-sheet dispensing keeps handling quick, cuts labour time and keeps consumption under control. Tough, non-stick and tear-resistant, it is the professional choice for fresh-food weighing, kitchen prep, industrial repacking and high-volume retail counters.</t>
-  </si>
-  <si>
     <t>封面-Scale Sheet.png</t>
   </si>
   <si>
@@ -238,6 +223,22 @@
   </si>
   <si>
     <t>Masking protection, Disinfection screening, Dust cover, Fast application</t>
+  </si>
+  <si>
+    <t>Scale Sheet(Tare Sheet)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>結合集團專利技術打造的抽取式 Scale Sheet，突破傳統取用方式的繁瑣與不便。採用貼心的單張抽取設計，取用俐落、操作便利，不僅能提升作業效率、節省取用時間，更能有效控管使用成本。材質強韌、防沾黏且不易受污染，適用於生鮮秤重、餐飲備料、工業分裝及各大商場櫃台等多元作業場景，是追求高效率、衛生與便利性的專業首選。</t>
+  </si>
+  <si>
+    <t>Featuring the Group’s patented pull-out technology, Scale Sheet offers a smarter and more convenient alternative to traditional dispensing methods. Its easy-to-use single-sheet dispensing design allows for quick and efficient access, helping save valuable operation time while providing better control over material usage and costs. Durable, non-stick, and resistant to contamination, Scale Sheet is ideal for fresh food weighing, food preparation, industrial packaging, and retail counter operations, making it a professional choice for businesses seeking greater efficiency, hygiene, and convenience.</t>
+  </si>
+  <si>
+    <t>集團專利單張抽取設計｜取用便利・不易污染・衛生安心</t>
+  </si>
+  <si>
+    <t>Patented Single-Sheet Dispensing | Easy to Use, Reduced Contamination, Improved Hygiene</t>
   </si>
 </sst>
 </file>
@@ -683,214 +684,215 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" s="2" customFormat="1" ht="78" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" s="2" customFormat="1" ht="97.2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="2" customFormat="1" ht="78" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="2" customFormat="1" ht="78" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="2" customFormat="1" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="2" customFormat="1" ht="78" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="I6" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="2" customFormat="1" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="I7" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="2" customFormat="1" ht="78" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="H8" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="I8" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:I8" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:I1 A3:I8 G2:I2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/src/data/products-data.xlsx
+++ b/src/data/products-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lyanc\VScodeProgram\inteplast_home_page_tw\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51D752CB-EF9D-4A90-800A-0778F44FE35A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07C97469-AD6C-4A19-9645-FDAA6C8A871C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -93,9 +93,6 @@
     <t>清潔袋</t>
   </si>
   <si>
-    <t>Can Liners</t>
-  </si>
-  <si>
     <t>強韌耐穿刺、滴水不漏的日常清潔首選</t>
   </si>
   <si>
@@ -114,9 +111,6 @@
     <t>連捲、單張抽取、八折袋、環保清潔袋</t>
   </si>
   <si>
-    <t>Perforated roll, Single-sheet dispensing, Eight-fold gusseted bag, Green Mark liner</t>
-  </si>
-  <si>
     <t>拉繩袋</t>
   </si>
   <si>
@@ -225,20 +219,29 @@
     <t>Masking protection, Disinfection screening, Dust cover, Fast application</t>
   </si>
   <si>
-    <t>Scale Sheet(Tare Sheet)</t>
+    <t>結合集團專利技術打造的抽取式 Scale Sheet，突破傳統取用方式的繁瑣與不便。採用貼心的單張抽取設計，取用俐落、操作便利，不僅能提升作業效率、節省取用時間，更能有效控管使用成本。材質強韌、防沾黏且不易受污染，適用於生鮮秤重、餐飲備料、工業分裝及各大商場櫃台等多元作業場景，是追求高效率、衛生與便利性的專業首選。</t>
+  </si>
+  <si>
+    <t>Featuring the Group’s patented pull-out technology, Scale Sheet offers a smarter and more convenient alternative to traditional dispensing methods. Its easy-to-use single-sheet dispensing design allows for quick and efficient access, helping save valuable operation time while providing better control over material usage and costs. Durable, non-stick, and resistant to contamination, Scale Sheet is ideal for fresh food weighing, food preparation, industrial packaging, and retail counter operations, making it a professional choice for businesses seeking greater efficiency, hygiene, and convenience.</t>
+  </si>
+  <si>
+    <t>集團專利單張抽取設計｜取用便利・不易污染・衛生安心</t>
+  </si>
+  <si>
+    <t>Patented Single-Sheet Dispensing | Easy to Use, Reduced Contamination, Improved Hygiene</t>
+  </si>
+  <si>
+    <t>Garbage Bag</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>結合集團專利技術打造的抽取式 Scale Sheet，突破傳統取用方式的繁瑣與不便。採用貼心的單張抽取設計，取用俐落、操作便利，不僅能提升作業效率、節省取用時間，更能有效控管使用成本。材質強韌、防沾黏且不易受污染，適用於生鮮秤重、餐飲備料、工業分裝及各大商場櫃台等多元作業場景，是追求高效率、衛生與便利性的專業首選。</t>
-  </si>
-  <si>
-    <t>Featuring the Group’s patented pull-out technology, Scale Sheet offers a smarter and more convenient alternative to traditional dispensing methods. Its easy-to-use single-sheet dispensing design allows for quick and efficient access, helping save valuable operation time while providing better control over material usage and costs. Durable, non-stick, and resistant to contamination, Scale Sheet is ideal for fresh food weighing, food preparation, industrial packaging, and retail counter operations, making it a professional choice for businesses seeking greater efficiency, hygiene, and convenience.</t>
-  </si>
-  <si>
-    <t>集團專利單張抽取設計｜取用便利・不易污染・衛生安心</t>
-  </si>
-  <si>
-    <t>Patented Single-Sheet Dispensing | Easy to Use, Reduced Contamination, Improved Hygiene</t>
+    <t>Perforated roll, Single-sheet dispensing, Can Liners, ECO Garbage Bag</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Scale Sheet
+(Tare Sheet)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -686,22 +689,22 @@
     </row>
     <row r="2" spans="1:9" s="2" customFormat="1" ht="97.2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>69</v>
-      </c>
       <c r="D2" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>9</v>
@@ -747,144 +750,144 @@
         <v>21</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="I4" s="1" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="2" customFormat="1" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="2" customFormat="1" ht="78" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="I6" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="2" customFormat="1" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="I7" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="2" customFormat="1" ht="78" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="H8" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="I8" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -892,7 +895,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:I1 A3:I8 G2:I2" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:I1 A3:I3 G2:I2 A5:I8 A4 C4:H4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/src/data/products-data.xlsx
+++ b/src/data/products-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lyanc\VScodeProgram\inteplast_home_page_tw\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07C97469-AD6C-4A19-9645-FDAA6C8A871C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B033FE07-34D5-4CB3-87E2-9532C3AAB64E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -84,12 +84,6 @@
     <t>封面-蔬果袋.png</t>
   </si>
   <si>
-    <t>耐熱袋、雙道封口、食品袋、市場袋</t>
-  </si>
-  <si>
-    <t>Heat-resistant bag, Double seal, Food bag, Market bag</t>
-  </si>
-  <si>
     <t>清潔袋</t>
   </si>
   <si>
@@ -135,9 +129,6 @@
     <t>清潔袋、醫療袋、環保拉繩袋</t>
   </si>
   <si>
-    <t>Can liner, Medical waste bag, Eco draw tape liner</t>
-  </si>
-  <si>
     <t>多功能手套</t>
   </si>
   <si>
@@ -162,9 +153,6 @@
     <t>無粉末、無乳膠、內壓紋、易穿脫、彈性優、觸感佳</t>
   </si>
   <si>
-    <t>Powder-free, Latex-free, Embossed texture, Easy on/off, High elasticity, Soft feel</t>
-  </si>
-  <si>
     <t>夾鏈袋</t>
   </si>
   <si>
@@ -187,9 +175,6 @@
   </si>
   <si>
     <t>密實袋、冷凍袋、夾鏈袋</t>
-  </si>
-  <si>
-    <t>Storage bag, Freezer bag, Zipper bag</t>
   </si>
   <si>
     <t>遮蔽防塵膠帶</t>
@@ -235,12 +220,32 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Perforated roll, Single-sheet dispensing, Can Liners, ECO Garbage Bag</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Scale Sheet
 (Tare Sheet)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Coreless roll, Interleaved, Can Liners, ECO Garbage Bag</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Powder-free, Latex-free, Embossed texture, Easy on/off, High elasticity, Soft feel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Garbage Bag, Healthcare Isolation Bag, Eco draw tape</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Slider Bag, Freezer Bag, Zipper Bag</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Heat-resistant bag, Double seal, Food bag, Market bag</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>耐熱袋、雙道封口、食品袋、市場袋、冰袋</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -689,22 +694,22 @@
     </row>
     <row r="2" spans="1:9" s="2" customFormat="1" ht="97.2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>9</v>
@@ -739,155 +744,155 @@
         <v>18</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>19</v>
+        <v>70</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="2" customFormat="1" ht="78" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="I4" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="2" customFormat="1" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="I5" s="1" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="2" customFormat="1" ht="78" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>44</v>
-      </c>
       <c r="I6" s="1" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="2" customFormat="1" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="I7" s="1" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="2" customFormat="1" ht="78" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="H8" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="I8" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -895,7 +900,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:I1 A3:I3 G2:I2 A5:I8 A4 C4:H4" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:I1 A3:G3 G2:I2 A8:I8 A4 C4:H4 A5:H5 A6:H6 A7:H7" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>